--- a/news_daily/2026-10-02.xlsx
+++ b/news_daily/2026-10-02.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -93,9 +88,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +518,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +823,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -991,6 +1007,10 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1153,6 +1173,10 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1331,705 +1355,789 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-10-02T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>You could get a payment from Equifax's $100M settlement</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNcWJpTnBfMHNISHdORmFrd3FkcGJyZWlJMG5wdTZtSHJPNjJMUEpaRTVHSTBqVUFlNDhuVFA0dXJnOGh4bDdpTmhJLUhKY2ZYektjY0VWMHhOaXk1dEs4WTh4eHd3bDNucUJWZlduak1YNFg4ZFhRVFRPVHhwUDQ1TF9ueFp6cUJQWHY4WE95eHY5aTJMZnhnUVhDUHpNVGxGcUFGSEJPcw?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>USA Today</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>00cd7151466c4cbc8d4e83f913784451</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>c07eee9d2610120a6a80119e</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>1cdffdc971753b247a8b729c</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>EFX-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNcWJpTnBfMHNISHdORmFrd3FkcGJyZWlJMG5wdTZtSHJPNjJMUEpaRTVHSTBqVUFlNDhuVFA0dXJnOGh4bDdpTmhJLUhKY2ZYektjY0VWMHhOaXk1dEs4WTh4eHd3bDNucUJWZlduak1YNFg4ZFhRVFRPVHhwUDQ1TF9ueFp6cUJQWHY4WE95eHY5aTJMZnhnUVhDUHpNVGxGcUFGSEJPcw?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>USA Today</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>c07eee9d2610120a6a80119e</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>1cdffdc971753b247a8b729c</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-02T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>$2.5 billion Amazon settlement: More payments being sent out, with another round possible</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.753</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZEhQM3p0VkRXeHdkNUIwbmpNZUJ1dkpfMjBCQUtLSmJTWTdBOWFMTThtdDZHUXVfQTVpck5Cd3A3bzd3LVdWVXhyM3RCM0dNaXNlRTBLYVE4RDVveko4VlRVc0xZNWU5VllRajR5bmZCMExiRlhvdmFlSkJEWVY0Q1duRU9jaDBjRURvTUcweW82QUU1ald2aXpld0t3VVVqUGE2Y1NMdi1NZVphdVhESkdjTXF6a0dGczVYSEd2WVo1UdIBxwFBVV95cUxNcmtkY1J4SGN4OVRFTGNHMHF3enA0SGR2dldtRXNxVmVoWGtmaERqa05wOTFtZlZkZEQwSUtSWjJTMUNGSGxuQU5TNVZLeWdKeFp0THpOandVMHp6dERjZTNEZ3FMRW5NUzRnMTdhRjZtVzJnTXp4b194cmpuY2ZtRnJYTDZGQ3NQaGYzTWxQbWxvZ1NCWlhHRURiMXRGcW92VExWWHBkaVdyeF96YkZDaVUtUWZxbmJveFkzM0FDb0RNWGNVaEN3?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>The Hill</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>cca43ddaa7fe4e60b0417b8eb04781ae</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>99b789193d9c49c431102462</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>f9ff2ff39de4628e589dff81</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>AMZN-REGULATORY_PENALTY-001</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.753</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZEhQM3p0VkRXeHdkNUIwbmpNZUJ1dkpfMjBCQUtLSmJTWTdBOWFMTThtdDZHUXVfQTVpck5Cd3A3bzd3LVdWVXhyM3RCM0dNaXNlRTBLYVE4RDVveko4VlRVc0xZNWU5VllRajR5bmZCMExiRlhvdmFlSkJEWVY0Q1duRU9jaDBjRURvTUcweW82QUU1ald2aXpld0t3VVVqUGE2Y1NMdi1NZVphdVhESkdjTXF6a0dGczVYSEd2WVo1UdIBxwFBVV95cUxNcmtkY1J4SGN4OVRFTGNHMHF3enA0SGR2dldtRXNxVmVoWGtmaERqa05wOTFtZlZkZEQwSUtSWjJTMUNGSGxuQU5TNVZLeWdKeFp0THpOandVMHp6dERjZTNEZ3FMRW5NUzRnMTdhRjZtVzJnTXp4b194cmpuY2ZtRnJYTDZGQ3NQaGYzTWxQbWxvZ1NCWlhHRURiMXRGcW92VExWWHBkaVdyeF96YkZDaVUtUWZxbmJveFkzM0FDb0RNWGNVaEN3?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>The Hill</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>99b789193d9c49c431102462</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>f9ff2ff39de4628e589dff81</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>AMZN-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr"/>
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr"/>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr"/>
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>ADM</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Archer Daniels Midland</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-10-02T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>CJ CheilJedang and ADM to Form New Joint Venture to Strengthen Amino Acid Production and Supply Chains</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>供應鏈中斷</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>0.911</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPX3FKVkVYNWJGQ0xzMm1NMEowZ1VDeVZodFBNSmIxNnEtT1JCY3dTNXpDTGppREpqMHdlM3VHTUN3WDdjM1BHM2UtSjJ4QTM4M1l3LWhBcURGWGMzZzk1Z3RoTEJ2Ry1RcTUxYjZrT2JvZTdrckNBZmdGNWNRek5kMUFTbVJCOEV0M2NqWFBqY2tDbERUTnpKQ0FUaUdxZnN4?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>SUPPLY_CHAIN_DISRUPTION</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>supply chain</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>6c154d4ac0739d8781bb4957</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AD7" s="3" t="inlineStr">
         <is>
           <t>ae567009a74f648eed90d5a3</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AE7" s="3" t="inlineStr">
         <is>
           <t>ADM-SUPPLY_CHAIN_DISRUPTION-001</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr"/>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr"/>
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
         <is>
           <t>ADM</t>
         </is>
       </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="4" t="inlineStr"/>
-      <c r="BG7" s="4" t="inlineStr">
+      <c r="BF7" s="3" t="inlineStr"/>
+      <c r="BG7" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>First Solar</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-02T06:05:02+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>第一太陽能起訴中國JA Solar侵犯專利權</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-FSLR/news/</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>起訴</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>48b69c97770e4a959b0adeea30ad3f6c</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>1e0696196765e7a589ff576e</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>49ef3f5655e631c8b912a1fe</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>FSLR-MAJOR_LITIGATION-001</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr"/>
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-FSLR/news/</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>起訴</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>1e0696196765e7a589ff576e</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>49ef3f5655e631c8b912a1fe</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr">
-        <is>
-          <t>FSLR-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr">
         <is>
           <t>FSLR</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr"/>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BG8" s="2" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH8"/>
+  <autoFilter ref="A1:BL8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2040,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2103,6 +2211,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2406,6 +2518,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2420,12 +2552,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Equifax, Inc. Common Stock</t>
+          <t>Archer Daniels Midland</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2435,23 +2567,23 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>You could get a payment from Equifax's $100M settlement</t>
+          <t>CJ CheilJedang and ADM to Form New Joint Venture to Strengthen Amino Acid Production and Supply Chains</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>供應鏈中斷</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -2472,7 +2604,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.911</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -2486,28 +2618,28 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNcWJpTnBfMHNISHdORmFrd3FkcGJyZWlJMG5wdTZtSHJPNjJMUEpaRTVHSTBqVUFlNDhuVFA0dXJnOGh4bDdpTmhJLUhKY2ZYektjY0VWMHhOaXk1dEs4WTh4eHd3bDNucUJWZlduak1YNFg4ZFhRVFRPVHhwUDQ1TF9ueFp6cUJQWHY4WE95eHY5aTJMZnhnUVhDUHpNVGxGcUFGSEJPcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPX3FKVkVYNWJGQ0xzMm1NMEowZ1VDeVZodFBNSmIxNnEtT1JCY3dTNXpDTGppREpqMHdlM3VHTUN3WDdjM1BHM2UtSjJ4QTM4M1l3LWhBcURGWGMzZzk1Z3RoTEJ2Ry1RcTUxYjZrT2JvZTdrckNBZmdGNWNRek5kMUFTbVJCOEV0M2NqWFBqY2tDbERUTnpKQ0FUaUdxZnN4?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>USA Today</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr"/>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>supply chain</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
@@ -2518,17 +2650,17 @@
       <c r="AB2" s="3" t="inlineStr"/>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>c07eee9d2610120a6a80119e</t>
+          <t>6c154d4ac0739d8781bb4957</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>1cdffdc971753b247a8b729c</t>
+          <t>ae567009a74f648eed90d5a3</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr">
         <is>
-          <t>EFX-REGULATORY_PENALTY-001</t>
+          <t>ADM-SUPPLY_CHAIN_DISRUPTION-001</t>
         </is>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
@@ -2548,18 +2680,14 @@
       <c r="AT2" s="3" t="inlineStr"/>
       <c r="AU2" s="3" t="inlineStr"/>
       <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW2" s="3" t="inlineStr"/>
       <c r="AX2" s="3" t="inlineStr"/>
       <c r="AY2" s="3" t="inlineStr"/>
       <c r="AZ2" s="3" t="inlineStr"/>
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
@@ -2570,541 +2698,23 @@
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr"/>
       <c r="BG2" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>$2.5 billion Amazon settlement: More payments being sent out, with another round possible</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0.753</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZEhQM3p0VkRXeHdkNUIwbmpNZUJ1dkpfMjBCQUtLSmJTWTdBOWFMTThtdDZHUXVfQTVpck5Cd3A3bzd3LVdWVXhyM3RCM0dNaXNlRTBLYVE4RDVveko4VlRVc0xZNWU5VllRajR5bmZCMExiRlhvdmFlSkJEWVY0Q1duRU9jaDBjRURvTUcweW82QUU1ald2aXpld0t3VVVqUGE2Y1NMdi1NZVphdVhESkdjTXF6a0dGczVYSEd2WVo1UdIBxwFBVV95cUxNcmtkY1J4SGN4OVRFTGNHMHF3enA0SGR2dldtRXNxVmVoWGtmaERqa05wOTFtZlZkZEQwSUtSWjJTMUNGSGxuQU5TNVZLeWdKeFp0THpOandVMHp6dERjZTNEZ3FMRW5NUzRnMTdhRjZtVzJnTXp4b194cmpuY2ZtRnJYTDZGQ3NQaGYzTWxQbWxvZ1NCWlhHRURiMXRGcW92VExWWHBkaVdyeF96YkZDaVUtUWZxbmJveFkzM0FDb0RNWGNVaEN3?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>The Hill</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>99b789193d9c49c431102462</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>f9ff2ff39de4628e589dff81</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>AMZN-REGULATORY_PENALTY-001</t>
-        </is>
-      </c>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr"/>
-      <c r="BG3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Archer Daniels Midland</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>CJ CheilJedang and ADM to Form New Joint Venture to Strengthen Amino Acid Production and Supply Chains</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0.911</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPX3FKVkVYNWJGQ0xzMm1NMEowZ1VDeVZodFBNSmIxNnEtT1JCY3dTNXpDTGppREpqMHdlM3VHTUN3WDdjM1BHM2UtSjJ4QTM4M1l3LWhBcURGWGMzZzk1Z3RoTEJ2Ry1RcTUxYjZrT2JvZTdrckNBZmdGNWNRek5kMUFTbVJCOEV0M2NqWFBqY2tDbERUTnpKQ0FUaUdxZnN4?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>6c154d4ac0739d8781bb4957</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>ae567009a74f648eed90d5a3</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr">
-        <is>
-          <t>ADM-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>First Solar</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T06:05:02+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>第一太陽能起訴中國JA Solar侵犯專利權</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-FSLR/news/</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>起訴</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>1e0696196765e7a589ff576e</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>49ef3f5655e631c8b912a1fe</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr">
-        <is>
-          <t>FSLR-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="3" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
-      <c r="BE5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="3" t="inlineStr"/>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH5"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3115,7 +2725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3178,6 +2788,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3481,187 +3095,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>First Solar</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T06:05:02+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>第一太陽能起訴中國JA Solar侵犯專利權</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-FSLR/news/</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>起訴</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>1e0696196765e7a589ff576e</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>49ef3f5655e631c8b912a1fe</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr">
-        <is>
-          <t>FSLR-MAJOR_LITIGATION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
-      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3672,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3735,6 +3191,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4038,9 +3498,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4051,7 +3531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4101,134 +3581,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4238,46 +3718,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4286,12 +3800,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4301,90 +3815,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4394,94 +3912,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4489,89 +4007,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-02.xlsx
+++ b/news_daily/2026-10-02.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,15 +74,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1765,178 +1757,202 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>ADM</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Archer Daniels Midland</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-10-02T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>CJ CheilJedang and ADM to Form New Joint Venture to Strengthen Amino Acid Production and Supply Chains</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.911</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPX3FKVkVYNWJGQ0xzMm1NMEowZ1VDeVZodFBNSmIxNnEtT1JCY3dTNXpDTGppREpqMHdlM3VHTUN3WDdjM1BHM2UtSjJ4QTM4M1l3LWhBcURGWGMzZzk1Z3RoTEJ2Ry1RcTUxYjZrT2JvZTdrckNBZmdGNWNRek5kMUFTbVJCOEV0M2NqWFBqY2tDbERUTnpKQ0FUaUdxZnN4?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>7ebf9e9c9a644331b67b19f69540d1ab</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>6c154d4ac0739d8781bb4957</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>ae567009a74f648eed90d5a3</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>ADM-SUPPLY_CHAIN_DISRUPTION-001</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>0.911</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPX3FKVkVYNWJGQ0xzMm1NMEowZ1VDeVZodFBNSmIxNnEtT1JCY3dTNXpDTGppREpqMHdlM3VHTUN3WDdjM1BHM2UtSjJ4QTM4M1l3LWhBcURGWGMzZzk1Z3RoTEJ2Ry1RcTUxYjZrT2JvZTdrckNBZmdGNWNRek5kMUFTbVJCOEV0M2NqWFBqY2tDbERUTnpKQ0FUaUdxZnN4?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>6c154d4ac0739d8781bb4957</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>ae567009a74f648eed90d5a3</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr">
-        <is>
-          <t>ADM-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr"/>
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
         <is>
           <t>ADM</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BF7" s="2" t="inlineStr"/>
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2148,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2539,182 +2555,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Archer Daniels Midland</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>CJ CheilJedang and ADM to Form New Joint Venture to Strengthen Amino Acid Production and Supply Chains</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>0.911</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPX3FKVkVYNWJGQ0xzMm1NMEowZ1VDeVZodFBNSmIxNnEtT1JCY3dTNXpDTGppREpqMHdlM3VHTUN3WDdjM1BHM2UtSjJ4QTM4M1l3LWhBcURGWGMzZzk1Z3RoTEJ2Ry1RcTUxYjZrT2JvZTdrckNBZmdGNWNRek5kMUFTbVJCOEV0M2NqWFBqY2tDbERUTnpKQ0FUaUdxZnN4?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>6c154d4ac0739d8781bb4957</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>ae567009a74f648eed90d5a3</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr">
-        <is>
-          <t>ADM-SUPPLY_CHAIN_DISRUPTION-001</t>
-        </is>
-      </c>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr"/>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr"/>
-      <c r="BG2" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
-      <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-02.xlsx
+++ b/news_daily/2026-10-02.xlsx
@@ -1219,13 +1219,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1278,7 +1282,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>c2467e40dc754f83b6a9f76488bc405c</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>141f50989a8e411bb6c6de39</t>
@@ -1303,7 +1311,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1349,8 +1361,16 @@
       <c r="BH4" s="2" t="inlineStr"/>
       <c r="BI4" s="2" t="inlineStr"/>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">

--- a/news_daily/2026-10-02.xlsx
+++ b/news_daily/2026-10-02.xlsx
@@ -890,7 +890,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -946,7 +950,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>06f3a725cae64a53af9ace3dd311a791</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>74b0224c1db1e0cbe8cc051c</t>
@@ -971,7 +979,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1001,8 +1013,16 @@
       </c>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1056,7 +1076,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -1112,7 +1136,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>726a042f6e00434cb10e959481236432</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>74b0224c1db1e0cbe8cc051c</t>
@@ -1137,7 +1165,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1167,8 +1199,16 @@
       </c>
       <c r="BI3" s="2" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
